--- a/artfynd/A 35788-2021 artfynd.xlsx
+++ b/artfynd/A 35788-2021 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126411320</v>
+        <v>126411329</v>
       </c>
       <c r="B3" t="n">
-        <v>5176</v>
+        <v>91207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,36 +805,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,7 +838,7 @@
         <v>6804385</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126411329</v>
+        <v>126411320</v>
       </c>
       <c r="B4" t="n">
-        <v>91207</v>
+        <v>5176</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,26 +915,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>6804385</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 35788-2021 artfynd.xlsx
+++ b/artfynd/A 35788-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126411346</v>
       </c>
       <c r="B2" t="n">
-        <v>98386</v>
+        <v>98395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126411329</v>
+        <v>126411320</v>
       </c>
       <c r="B3" t="n">
-        <v>91207</v>
+        <v>5176</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,26 +805,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,7 +848,7 @@
         <v>6804385</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126411320</v>
+        <v>126411329</v>
       </c>
       <c r="B4" t="n">
-        <v>5176</v>
+        <v>91210</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,36 +925,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>6804385</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,7 +1027,7 @@
         <v>126411334</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35788-2021 artfynd.xlsx
+++ b/artfynd/A 35788-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126411346</v>
+        <v>126411329</v>
       </c>
       <c r="B2" t="n">
-        <v>98395</v>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,35 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -728,7 +719,7 @@
         <v>6804385</v>
       </c>
       <c r="S2" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +788,7 @@
         <v>126411320</v>
       </c>
       <c r="B3" t="n">
-        <v>5176</v>
+        <v>5179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126411329</v>
+        <v>126411334</v>
       </c>
       <c r="B4" t="n">
-        <v>91210</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,26 +916,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1024,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126411334</v>
+        <v>126411346</v>
       </c>
       <c r="B5" t="n">
-        <v>98278</v>
+        <v>99153</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,25 +1027,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1069,7 +1069,7 @@
         <v>6804385</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
